--- a/docs/downloads/05/tbl_water_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/05/tbl_water_marovoay_madiromiongana.xlsx
@@ -405,12 +405,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -531,12 +513,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -548,12 +524,6 @@
         <is>
           <t>Impluvium</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
       </c>
     </row>
     <row r="12">
